--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.86690005055635</v>
+        <v>9.240871258215408</v>
       </c>
       <c r="D2" t="n">
-        <v>56.74588771939415</v>
+        <v>9.22120675440155</v>
       </c>
       <c r="E2" t="n">
-        <v>3.654822228637556</v>
+        <v>0.5939086121536032</v>
       </c>
       <c r="F2" t="n">
-        <v>3.63925062274328</v>
+        <v>0.5913782261957827</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.55725559328124</v>
+        <v>8.053054033908202</v>
       </c>
       <c r="D3" t="n">
-        <v>49.4673864739076</v>
+        <v>8.038450302009984</v>
       </c>
       <c r="E3" t="n">
-        <v>3.654822228637556</v>
+        <v>0.5939086121536032</v>
       </c>
       <c r="F3" t="n">
-        <v>3.63925062274328</v>
+        <v>0.5913782261957827</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
